--- a/Data/g10.1.xlsx
+++ b/Data/g10.1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,13 +455,13 @@
         <v>2012</v>
       </c>
       <c r="B2" t="n">
-        <v>-6.94411181458936</v>
+        <v>-6.943915584411064</v>
       </c>
       <c r="C2" t="n">
-        <v>8.002699504927225</v>
+        <v>8.063836520581003</v>
       </c>
       <c r="D2" t="n">
-        <v>3.559809995278185</v>
+        <v>3.559325396467528</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2013</v>
       </c>
       <c r="B3" t="n">
-        <v>-3.034807695923036</v>
+        <v>-3.056737098793627</v>
       </c>
       <c r="C3" t="n">
-        <v>4.323030226531244</v>
+        <v>4.291227331894065</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.227979871290955</v>
+        <v>-5.227518314651459</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>2014</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.2285639026915365</v>
+        <v>-0.1444867084375634</v>
       </c>
       <c r="C4" t="n">
-        <v>4.082587020578132</v>
+        <v>4.227574015790947</v>
       </c>
       <c r="D4" t="n">
-        <v>1.619966974719511</v>
+        <v>1.618229603728349</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>2015</v>
       </c>
       <c r="B5" t="n">
-        <v>1.249666286568085</v>
+        <v>1.254511464850383</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.211081365207844</v>
+        <v>-1.288952853883651</v>
       </c>
       <c r="D5" t="n">
-        <v>8.071189693001756</v>
+        <v>8.070099777843897</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>2016</v>
       </c>
       <c r="B6" t="n">
-        <v>-5.144988776136906</v>
+        <v>-5.152998853751356</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.644488712179317</v>
+        <v>-3.641790557912783</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1792322793926937</v>
+        <v>0.1728163876709266</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>2017</v>
       </c>
       <c r="B7" t="n">
-        <v>-3.393663968685923</v>
+        <v>-3.475274044690935</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6064994933137724</v>
+        <v>0.5934860075108572</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7544524441076339</v>
+        <v>0.7246132344012723</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>2018</v>
       </c>
       <c r="B8" t="n">
-        <v>-3.189605498522374</v>
+        <v>-3.274639305111249</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.101825692711189</v>
+        <v>-1.040992008671504</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.923380893200122</v>
+        <v>-1.952200894635903</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>2019</v>
       </c>
       <c r="B9" t="n">
-        <v>2.96747992846258</v>
+        <v>2.903384808201515</v>
       </c>
       <c r="C9" t="n">
-        <v>1.029256131383471</v>
+        <v>0.990254761787468</v>
       </c>
       <c r="D9" t="n">
-        <v>9.604233041845811</v>
+        <v>9.570886459072515</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>2020</v>
       </c>
       <c r="B10" t="n">
-        <v>-13.97396110968855</v>
+        <v>-14.04055133510078</v>
       </c>
       <c r="C10" t="n">
-        <v>-3.939015861750861</v>
+        <v>-3.886771182327098</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.1555664716273</v>
+        <v>-12.16445581565237</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>2021</v>
       </c>
       <c r="B11" t="n">
-        <v>-11.05841606423861</v>
+        <v>-11.09566592487263</v>
       </c>
       <c r="C11" t="n">
-        <v>15.40055949980328</v>
+        <v>15.45169199659402</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.11367098522576</v>
+        <v>-14.10873045401769</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>2022</v>
       </c>
       <c r="B12" t="n">
-        <v>-4.760005733204464</v>
+        <v>-4.799471022048929</v>
       </c>
       <c r="C12" t="n">
-        <v>14.550983425704</v>
+        <v>14.6415720152125</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.9284390437578</v>
+        <v>-12.91860823981727</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,27 @@
         <v>2023</v>
       </c>
       <c r="B13" t="n">
-        <v>-6.021318115680419</v>
+        <v>-6.071197973946873</v>
       </c>
       <c r="C13" t="n">
-        <v>7.610411375818282</v>
+        <v>7.726692972933891</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.524579134993859</v>
+        <v>-7.513641631342683</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-6.772404990299218</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7.590981777713424</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-7.203737654062515</v>
       </c>
     </row>
   </sheetData>
